--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120805255</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120805255</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,5214 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129725915</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>456245</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6795972</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129725923</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>456270</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6795982</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129725993</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>456038</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6795840</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129725992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456023</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6795818</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129725996</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456173</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6795980</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129725917</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456248</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6796057</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129725948</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456265</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6796033</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129725955</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>456307</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6795993</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129725985</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>456242</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6795974</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129725934</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>456358</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6796007</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129725954</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>456347</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6796030</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129725961</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>456325</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6796001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129725918</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>456327</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6796090</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129725981</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>456260</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6796058</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129725916</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>456252</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6795977</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129725956</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>456275</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6795967</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129725930</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>456248</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6795998</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129725951</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>456335</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6796044</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129725919</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>456333</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6796026</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129725953</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>456343</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6796032</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129725994</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>456022</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6795956</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129725952</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>456328</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6796020</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129726002</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>456047</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6795976</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129725973</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>456117</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6795876</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129725984</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>456330</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6795990</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129725982</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>456287</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6796072</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129725933</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>456029</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6795960</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129725997</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>456179</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6795973</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129725957</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>456253</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6795980</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129725960</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78832</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>456343</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6796050</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129725988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>456109</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6796001</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129725940</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>456159</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6796000</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129725941</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>456325</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6796048</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129725938</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>456346</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6796076</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129725950</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>456341</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6796057</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129725979</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>456029</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6795946</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129725929</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>456209</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6796011</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129725975</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>456012</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6795798</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129725928</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>456207</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6796000</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129725922</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>456327</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6795987</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129725959</v>
+      </c>
+      <c r="B43" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>456177</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6795973</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129725995</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>456299</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6795964</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129725987</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>456158</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6795973</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129725942</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>456107</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6795991</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129725921</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>456352</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6796004</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129725920</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>456344</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6795995</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129725958</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>456178</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6795996</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129725924</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>456237</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6795975</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129725983</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>456325</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6796071</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129725939</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>456003</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6795938</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129725986</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>456176</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6795998</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725915</v>
+        <v>129725993</v>
       </c>
       <c r="B3" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,34 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456245</v>
+        <v>456038</v>
       </c>
       <c r="R3" t="n">
-        <v>6795972</v>
+        <v>6795840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +865,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725923</v>
+        <v>129725992</v>
       </c>
       <c r="B4" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456270</v>
+        <v>456023</v>
       </c>
       <c r="R4" t="n">
-        <v>6795982</v>
+        <v>6795818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +971,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725993</v>
+        <v>129725996</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456038</v>
+        <v>456173</v>
       </c>
       <c r="R5" t="n">
-        <v>6795840</v>
+        <v>6795980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1118,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R6" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,18 +1180,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R7" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,18 +1277,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1301,45 +1301,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725917</v>
+        <v>129725948</v>
       </c>
       <c r="B8" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456248</v>
+        <v>456265</v>
       </c>
       <c r="R8" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,54 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725948</v>
+        <v>129725917</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456265</v>
+        <v>456248</v>
       </c>
       <c r="R9" t="n">
-        <v>6796033</v>
+        <v>6796057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1487,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>129725985</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129725934</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,54 +1823,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725954</v>
+        <v>129725981</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456347</v>
+        <v>456260</v>
       </c>
       <c r="R13" t="n">
-        <v>6796030</v>
+        <v>6796058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1933,7 +1923,7 @@
         <v>129725961</v>
       </c>
       <c r="B14" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,7 +2020,7 @@
         <v>129725918</v>
       </c>
       <c r="B15" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725981</v>
+        <v>129725916</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,21 +2125,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456260</v>
+        <v>456252</v>
       </c>
       <c r="R16" t="n">
-        <v>6796058</v>
+        <v>6795977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,45 +2211,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725916</v>
+        <v>129725954</v>
       </c>
       <c r="B17" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456252</v>
+        <v>456347</v>
       </c>
       <c r="R17" t="n">
-        <v>6795977</v>
+        <v>6796030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,6 +2299,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>129725930</v>
       </c>
       <c r="B19" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725984</v>
+        <v>129725933</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,26 +3261,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456330</v>
+        <v>456029</v>
       </c>
       <c r="R27" t="n">
-        <v>6795990</v>
+        <v>6795960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,18 +3331,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725982</v>
+        <v>129725984</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456287</v>
+        <v>456330</v>
       </c>
       <c r="R28" t="n">
-        <v>6796072</v>
+        <v>6795990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3462,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725933</v>
+        <v>129725982</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3473,31 +3472,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3505,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456029</v>
+        <v>456287</v>
       </c>
       <c r="R29" t="n">
-        <v>6795960</v>
+        <v>6796072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,12 +3537,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725960</v>
+        <v>129725940</v>
       </c>
       <c r="B32" t="n">
-        <v>78832</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,34 +3782,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456343</v>
+        <v>456159</v>
       </c>
       <c r="R32" t="n">
-        <v>6796050</v>
+        <v>6796000</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3887,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R33" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3965,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725940</v>
+        <v>129725988</v>
       </c>
       <c r="B34" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,42 +3984,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456159</v>
+        <v>456109</v>
       </c>
       <c r="R34" t="n">
-        <v>6796000</v>
+        <v>6796001</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725941</v>
+        <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,42 +4081,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456325</v>
+        <v>456029</v>
       </c>
       <c r="R35" t="n">
-        <v>6796048</v>
+        <v>6795946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725938</v>
+        <v>129725941</v>
       </c>
       <c r="B36" t="n">
-        <v>57895</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,21 +4178,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,7 +4200,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4218,10 +4210,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456346</v>
+        <v>456325</v>
       </c>
       <c r="R36" t="n">
-        <v>6796076</v>
+        <v>6796048</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,41 +4272,40 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725950</v>
+        <v>129725938</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4324,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456341</v>
+        <v>456346</v>
       </c>
       <c r="R37" t="n">
-        <v>6796057</v>
+        <v>6796076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4359,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4387,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725979</v>
+        <v>129725929</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4398,21 +4388,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456029</v>
+        <v>456209</v>
       </c>
       <c r="R38" t="n">
-        <v>6795946</v>
+        <v>6796011</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,45 +4474,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725929</v>
+        <v>129725950</v>
       </c>
       <c r="B39" t="n">
-        <v>79694</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456209</v>
+        <v>456341</v>
       </c>
       <c r="R39" t="n">
-        <v>6796011</v>
+        <v>6796057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,6 +4562,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>129725975</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129725928</v>
       </c>
       <c r="B41" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>129725922</v>
       </c>
       <c r="B42" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>129725995</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>129725987</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>129725942</v>
       </c>
       <c r="B46" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>129725921</v>
       </c>
       <c r="B47" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129725920</v>
       </c>
       <c r="B48" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5481,43 +5481,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725958</v>
+        <v>129725983</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5525,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456178</v>
+        <v>456325</v>
       </c>
       <c r="R49" t="n">
-        <v>6795996</v>
+        <v>6796071</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5561,6 +5555,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,7 +5590,7 @@
         <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5685,37 +5684,43 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725983</v>
+        <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5723,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456325</v>
+        <v>456178</v>
       </c>
       <c r="R51" t="n">
-        <v>6796071</v>
+        <v>6795996</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,11 +5764,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5794,7 +5794,7 @@
         <v>129725939</v>
       </c>
       <c r="B52" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>129725986</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -1505,43 +1505,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725955</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1549,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456307</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6795993</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,6 +1579,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,26 +1622,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1650,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R11" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,18 +1692,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1718,40 +1716,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725934</v>
+        <v>129725955</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1761,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456358</v>
+        <v>456307</v>
       </c>
       <c r="R12" t="n">
-        <v>6796007</v>
+        <v>6795993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,6 +1804,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2629,45 +2629,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B21" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R21" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,6 +2717,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,54 +2736,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R22" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2815,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4775,45 +4775,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725922</v>
+        <v>129725959</v>
       </c>
       <c r="B42" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456327</v>
+        <v>456177</v>
       </c>
       <c r="R42" t="n">
-        <v>6795987</v>
+        <v>6795973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,6 +4863,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4872,54 +4882,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725959</v>
+        <v>129725922</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>79695</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456177</v>
+        <v>456327</v>
       </c>
       <c r="R43" t="n">
-        <v>6795973</v>
+        <v>6795987</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,7 +4961,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725993</v>
+        <v>129725915</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,37 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456038</v>
+        <v>456245</v>
       </c>
       <c r="R3" t="n">
-        <v>6795840</v>
+        <v>6795972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,18 +862,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725992</v>
+        <v>129725923</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456023</v>
+        <v>456270</v>
       </c>
       <c r="R4" t="n">
-        <v>6795818</v>
+        <v>6795982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,18 +959,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725996</v>
+        <v>129725993</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456173</v>
+        <v>456038</v>
       </c>
       <c r="R5" t="n">
-        <v>6795980</v>
+        <v>6795840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725915</v>
+        <v>129725992</v>
       </c>
       <c r="B6" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,34 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456245</v>
+        <v>456023</v>
       </c>
       <c r="R6" t="n">
-        <v>6795972</v>
+        <v>6795818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,12 +1165,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725923</v>
+        <v>129725996</v>
       </c>
       <c r="B7" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456270</v>
+        <v>456173</v>
       </c>
       <c r="R7" t="n">
-        <v>6795982</v>
+        <v>6795980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1271,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1301,54 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725948</v>
+        <v>129725917</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456265</v>
+        <v>456248</v>
       </c>
       <c r="R8" t="n">
-        <v>6796033</v>
+        <v>6796057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1408,45 +1398,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725917</v>
+        <v>129725948</v>
       </c>
       <c r="B9" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456248</v>
+        <v>456265</v>
       </c>
       <c r="R9" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1486,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,26 +1516,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1586,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,40 +1610,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725934</v>
+        <v>129725955</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456358</v>
+        <v>456307</v>
       </c>
       <c r="R11" t="n">
-        <v>6796007</v>
+        <v>6795993</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1698,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1716,43 +1717,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725955</v>
+        <v>129725985</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456307</v>
+        <v>456242</v>
       </c>
       <c r="R12" t="n">
-        <v>6795993</v>
+        <v>6795974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725981</v>
+        <v>129725918</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456260</v>
+        <v>456327</v>
       </c>
       <c r="R13" t="n">
-        <v>6796058</v>
+        <v>6796090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129725961</v>
+        <v>129725916</v>
       </c>
       <c r="B14" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456325</v>
+        <v>456252</v>
       </c>
       <c r="R14" t="n">
-        <v>6796001</v>
+        <v>6795977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725918</v>
+        <v>129725961</v>
       </c>
       <c r="B15" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456327</v>
+        <v>456325</v>
       </c>
       <c r="R15" t="n">
-        <v>6796090</v>
+        <v>6796001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725916</v>
+        <v>129725981</v>
       </c>
       <c r="B16" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,21 +2125,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456252</v>
+        <v>456260</v>
       </c>
       <c r="R16" t="n">
-        <v>6795977</v>
+        <v>6796058</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,7 +2428,7 @@
         <v>129725930</v>
       </c>
       <c r="B19" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>129725919</v>
       </c>
       <c r="B22" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,45 +2833,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R23" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,54 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R24" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3019,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,43 +3037,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3081,10 +3075,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R25" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,6 +3111,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3144,37 +3143,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3182,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R26" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,11 +3223,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725933</v>
+        <v>129725984</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,31 +3261,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456029</v>
+        <v>456330</v>
       </c>
       <c r="R27" t="n">
-        <v>6795960</v>
+        <v>6795990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,12 +3326,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3355,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725984</v>
+        <v>129725982</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456330</v>
+        <v>456287</v>
       </c>
       <c r="R28" t="n">
-        <v>6795990</v>
+        <v>6796072</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3461,10 +3462,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725982</v>
+        <v>129725933</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,26 +3473,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3499,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456287</v>
+        <v>456029</v>
       </c>
       <c r="R29" t="n">
-        <v>6796072</v>
+        <v>6795960</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,18 +3543,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725940</v>
+        <v>129725960</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,42 +3782,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456159</v>
+        <v>456343</v>
       </c>
       <c r="R32" t="n">
-        <v>6796000</v>
+        <v>6796050</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725960</v>
+        <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3887,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3911,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456343</v>
+        <v>456109</v>
       </c>
       <c r="R33" t="n">
-        <v>6796050</v>
+        <v>6796001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725988</v>
+        <v>129725940</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,34 +3976,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456109</v>
+        <v>456159</v>
       </c>
       <c r="R34" t="n">
-        <v>6796001</v>
+        <v>6796000</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4073,7 +4073,7 @@
         <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4272,40 +4272,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725938</v>
+        <v>129725950</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4315,10 +4316,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456346</v>
+        <v>456341</v>
       </c>
       <c r="R37" t="n">
-        <v>6796076</v>
+        <v>6796057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4359,6 +4360,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4380,7 +4382,7 @@
         <v>129725929</v>
       </c>
       <c r="B38" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4474,41 +4476,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725950</v>
+        <v>129725938</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4518,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456341</v>
+        <v>456346</v>
       </c>
       <c r="R39" t="n">
-        <v>6796057</v>
+        <v>6796076</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,7 +4563,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129725975</v>
+        <v>129725928</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456012</v>
+        <v>456207</v>
       </c>
       <c r="R40" t="n">
-        <v>6795798</v>
+        <v>6796000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129725928</v>
+        <v>129725975</v>
       </c>
       <c r="B41" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456207</v>
+        <v>456012</v>
       </c>
       <c r="R41" t="n">
-        <v>6796000</v>
+        <v>6795798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,54 +4775,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725959</v>
+        <v>129725922</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456177</v>
+        <v>456327</v>
       </c>
       <c r="R42" t="n">
-        <v>6795973</v>
+        <v>6795987</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,7 +4854,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4882,45 +4872,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725922</v>
+        <v>129725959</v>
       </c>
       <c r="B43" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456327</v>
+        <v>456177</v>
       </c>
       <c r="R43" t="n">
-        <v>6795987</v>
+        <v>6795973</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,6 +4960,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>129725995</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>129725987</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>129725921</v>
       </c>
       <c r="B47" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129725920</v>
       </c>
       <c r="B48" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>129725983</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5587,45 +5587,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725924</v>
+        <v>129725958</v>
       </c>
       <c r="B50" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456237</v>
+        <v>456178</v>
       </c>
       <c r="R50" t="n">
-        <v>6795975</v>
+        <v>6795996</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5666,6 +5675,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,54 +5694,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R51" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5773,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>129725986</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,31 +1516,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1581,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,41 +1611,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725955</v>
+        <v>129725934</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456307</v>
+        <v>456358</v>
       </c>
       <c r="R11" t="n">
-        <v>6795993</v>
+        <v>6796007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1717,37 +1716,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725985</v>
+        <v>129725955</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456242</v>
+        <v>456307</v>
       </c>
       <c r="R12" t="n">
-        <v>6795974</v>
+        <v>6795993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,45 +1823,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725918</v>
+        <v>129725954</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456327</v>
+        <v>456347</v>
       </c>
       <c r="R13" t="n">
-        <v>6796090</v>
+        <v>6796030</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1911,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1920,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129725916</v>
+        <v>129725961</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,21 +1941,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456252</v>
+        <v>456325</v>
       </c>
       <c r="R14" t="n">
-        <v>6795977</v>
+        <v>6796001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725961</v>
+        <v>129725918</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456325</v>
+        <v>456327</v>
       </c>
       <c r="R15" t="n">
-        <v>6796001</v>
+        <v>6796090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,54 +2221,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725954</v>
+        <v>129725916</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456347</v>
+        <v>456252</v>
       </c>
       <c r="R17" t="n">
-        <v>6796030</v>
+        <v>6795977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,7 +2300,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R23" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2940,45 +2930,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R24" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,6 +3018,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,37 +3037,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>8439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3075,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R25" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,11 +3117,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,43 +3144,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3187,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R26" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,6 +3218,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725984</v>
+        <v>129725933</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,26 +3261,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456330</v>
+        <v>456029</v>
       </c>
       <c r="R27" t="n">
-        <v>6795990</v>
+        <v>6795960</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,18 +3331,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,7 +3355,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725982</v>
+        <v>129725984</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3394,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456287</v>
+        <v>456330</v>
       </c>
       <c r="R28" t="n">
-        <v>6796072</v>
+        <v>6795990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3462,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725933</v>
+        <v>129725982</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3473,31 +3472,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3505,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456029</v>
+        <v>456287</v>
       </c>
       <c r="R29" t="n">
-        <v>6795960</v>
+        <v>6796072</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,12 +3537,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4070,45 +4070,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725979</v>
+        <v>129725950</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456029</v>
+        <v>456341</v>
       </c>
       <c r="R35" t="n">
-        <v>6795946</v>
+        <v>6796057</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4149,6 +4158,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4167,10 +4177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725941</v>
+        <v>129725979</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,42 +4188,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456325</v>
+        <v>456029</v>
       </c>
       <c r="R36" t="n">
-        <v>6796048</v>
+        <v>6795946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,54 +4274,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725950</v>
+        <v>129725929</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456341</v>
+        <v>456209</v>
       </c>
       <c r="R37" t="n">
-        <v>6796057</v>
+        <v>6796011</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,7 +4353,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4379,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725929</v>
+        <v>129725941</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4390,34 +4382,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456209</v>
+        <v>456325</v>
       </c>
       <c r="R38" t="n">
-        <v>6796011</v>
+        <v>6796048</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129725928</v>
+        <v>129725975</v>
       </c>
       <c r="B40" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456207</v>
+        <v>456012</v>
       </c>
       <c r="R40" t="n">
-        <v>6796000</v>
+        <v>6795798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129725975</v>
+        <v>129725928</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456012</v>
+        <v>456207</v>
       </c>
       <c r="R41" t="n">
-        <v>6795798</v>
+        <v>6796000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129725921</v>
+        <v>129725920</v>
       </c>
       <c r="B47" t="n">
         <v>79700</v>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456352</v>
+        <v>456344</v>
       </c>
       <c r="R47" t="n">
-        <v>6796004</v>
+        <v>6795995</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129725920</v>
+        <v>129725921</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456344</v>
+        <v>456352</v>
       </c>
       <c r="R48" t="n">
-        <v>6795995</v>
+        <v>6796004</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5587,54 +5587,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R50" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5675,7 +5666,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5694,45 +5684,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725924</v>
+        <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456237</v>
+        <v>456178</v>
       </c>
       <c r="R51" t="n">
-        <v>6795975</v>
+        <v>6795996</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5772,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725915</v>
+        <v>129725993</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,34 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456245</v>
+        <v>456038</v>
       </c>
       <c r="R3" t="n">
-        <v>6795972</v>
+        <v>6795840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +865,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725923</v>
+        <v>129725992</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456270</v>
+        <v>456023</v>
       </c>
       <c r="R4" t="n">
-        <v>6795982</v>
+        <v>6795818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +971,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725993</v>
+        <v>129725996</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1021,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456038</v>
+        <v>456173</v>
       </c>
       <c r="R5" t="n">
-        <v>6795840</v>
+        <v>6795980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1118,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R6" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,18 +1180,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R7" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,18 +1277,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,26 +1516,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1586,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,31 +1621,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1654,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R11" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,12 +1686,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1823,54 +1823,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725954</v>
+        <v>129725981</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456347</v>
+        <v>456260</v>
       </c>
       <c r="R13" t="n">
-        <v>6796030</v>
+        <v>6796058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2027,7 +2017,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725918</v>
+        <v>129725916</v>
       </c>
       <c r="B15" t="n">
         <v>79700</v>
@@ -2062,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456327</v>
+        <v>456252</v>
       </c>
       <c r="R15" t="n">
-        <v>6796090</v>
+        <v>6795977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725981</v>
+        <v>129725918</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,21 +2125,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456260</v>
+        <v>456327</v>
       </c>
       <c r="R16" t="n">
-        <v>6796058</v>
+        <v>6796090</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,45 +2211,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725916</v>
+        <v>129725954</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456252</v>
+        <v>456347</v>
       </c>
       <c r="R17" t="n">
-        <v>6795977</v>
+        <v>6796030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,6 +2299,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2425,45 +2425,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725930</v>
+        <v>129725951</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456248</v>
+        <v>456335</v>
       </c>
       <c r="R19" t="n">
-        <v>6795998</v>
+        <v>6796044</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,6 +2513,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2522,54 +2532,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129725951</v>
+        <v>129725930</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456335</v>
+        <v>456248</v>
       </c>
       <c r="R20" t="n">
-        <v>6796044</v>
+        <v>6795998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,7 +2611,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2629,54 +2629,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R21" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2708,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2736,45 +2726,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R22" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,6 +2814,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3037,43 +3037,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3081,10 +3075,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R25" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,6 +3111,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3144,37 +3143,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3182,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R26" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,11 +3223,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725988</v>
+        <v>129725940</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,34 +3879,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456109</v>
+        <v>456159</v>
       </c>
       <c r="R33" t="n">
-        <v>6796001</v>
+        <v>6796000</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3965,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725940</v>
+        <v>129725988</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,42 +3984,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456159</v>
+        <v>456109</v>
       </c>
       <c r="R34" t="n">
-        <v>6796000</v>
+        <v>6796001</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4070,54 +4070,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725950</v>
+        <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456341</v>
+        <v>456029</v>
       </c>
       <c r="R35" t="n">
-        <v>6796057</v>
+        <v>6795946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,7 +4149,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4177,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725979</v>
+        <v>129725938</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4188,34 +4178,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456029</v>
+        <v>456346</v>
       </c>
       <c r="R36" t="n">
-        <v>6795946</v>
+        <v>6796076</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4371,40 +4369,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725941</v>
+        <v>129725950</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4414,10 +4413,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456325</v>
+        <v>456341</v>
       </c>
       <c r="R38" t="n">
-        <v>6796048</v>
+        <v>6796057</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,6 +4457,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725938</v>
+        <v>129725941</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,7 +4509,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456346</v>
+        <v>456325</v>
       </c>
       <c r="R39" t="n">
-        <v>6796076</v>
+        <v>6796048</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5481,37 +5481,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725983</v>
+        <v>129725958</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5519,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456325</v>
+        <v>456178</v>
       </c>
       <c r="R49" t="n">
-        <v>6796071</v>
+        <v>6795996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,11 +5561,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,10 +5588,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,34 +5599,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R50" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,12 +5664,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,54 +5694,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R51" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5773,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,31 +1516,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1581,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1621,26 +1622,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1648,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R11" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,18 +1692,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2425,54 +2425,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725951</v>
+        <v>129725930</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456335</v>
+        <v>456248</v>
       </c>
       <c r="R19" t="n">
-        <v>6796044</v>
+        <v>6795998</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,7 +2504,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2532,45 +2522,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129725930</v>
+        <v>129725951</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456248</v>
+        <v>456335</v>
       </c>
       <c r="R20" t="n">
-        <v>6795998</v>
+        <v>6796044</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2611,6 +2610,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2629,45 +2629,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R21" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,6 +2717,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,54 +2736,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R22" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2815,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725933</v>
+        <v>129725982</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,31 +3261,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456029</v>
+        <v>456287</v>
       </c>
       <c r="R27" t="n">
-        <v>6795960</v>
+        <v>6796072</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,12 +3326,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3461,10 +3462,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725982</v>
+        <v>129725933</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,26 +3473,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3499,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456287</v>
+        <v>456029</v>
       </c>
       <c r="R29" t="n">
-        <v>6796072</v>
+        <v>6795960</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,18 +3543,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3567,45 +3567,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R30" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3655,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3664,54 +3674,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R31" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3753,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725960</v>
+        <v>129725940</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,34 +3782,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456343</v>
+        <v>456159</v>
       </c>
       <c r="R32" t="n">
-        <v>6796050</v>
+        <v>6796000</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725940</v>
+        <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,42 +3887,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456159</v>
+        <v>456109</v>
       </c>
       <c r="R33" t="n">
-        <v>6796000</v>
+        <v>6796001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,21 +3984,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R34" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725938</v>
+        <v>129725929</v>
       </c>
       <c r="B36" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,42 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456346</v>
+        <v>456209</v>
       </c>
       <c r="R36" t="n">
-        <v>6796076</v>
+        <v>6796011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725929</v>
+        <v>129725941</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4283,34 +4275,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456209</v>
+        <v>456325</v>
       </c>
       <c r="R37" t="n">
-        <v>6796011</v>
+        <v>6796048</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,41 +4369,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725950</v>
+        <v>129725938</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4413,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456341</v>
+        <v>456346</v>
       </c>
       <c r="R38" t="n">
-        <v>6796057</v>
+        <v>6796076</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,7 +4456,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4476,40 +4474,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725941</v>
+        <v>129725950</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4519,10 +4518,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456325</v>
+        <v>456341</v>
       </c>
       <c r="R39" t="n">
-        <v>6796048</v>
+        <v>6796057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,6 +4562,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5481,43 +5481,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725958</v>
+        <v>129725983</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5525,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456178</v>
+        <v>456325</v>
       </c>
       <c r="R49" t="n">
-        <v>6795996</v>
+        <v>6796071</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5561,6 +5555,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5588,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725983</v>
+        <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,37 +5598,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456325</v>
+        <v>456237</v>
       </c>
       <c r="R50" t="n">
-        <v>6796071</v>
+        <v>6795975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5664,18 +5660,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5694,45 +5684,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725924</v>
+        <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456237</v>
+        <v>456178</v>
       </c>
       <c r="R51" t="n">
-        <v>6795975</v>
+        <v>6795996</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5772,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -1301,45 +1301,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725917</v>
+        <v>129725948</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456248</v>
+        <v>456265</v>
       </c>
       <c r="R8" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,54 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725948</v>
+        <v>129725917</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456265</v>
+        <v>456248</v>
       </c>
       <c r="R9" t="n">
-        <v>6796033</v>
+        <v>6796057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1487,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,26 +1516,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1586,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,40 +1610,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725934</v>
+        <v>129725955</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456358</v>
+        <v>456307</v>
       </c>
       <c r="R11" t="n">
-        <v>6796007</v>
+        <v>6795993</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1698,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1716,43 +1717,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725955</v>
+        <v>129725985</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456307</v>
+        <v>456242</v>
       </c>
       <c r="R12" t="n">
-        <v>6795993</v>
+        <v>6795974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,45 +1823,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725981</v>
+        <v>129725954</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456260</v>
+        <v>456347</v>
       </c>
       <c r="R13" t="n">
-        <v>6796058</v>
+        <v>6796030</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1911,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2017,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725916</v>
+        <v>129725981</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456252</v>
+        <v>456260</v>
       </c>
       <c r="R15" t="n">
-        <v>6795977</v>
+        <v>6796058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,54 +2221,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725954</v>
+        <v>129725916</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456347</v>
+        <v>456252</v>
       </c>
       <c r="R17" t="n">
-        <v>6796030</v>
+        <v>6795977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,7 +2300,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2629,54 +2629,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R21" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2708,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2736,45 +2726,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R22" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,6 +2814,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3037,37 +3037,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>8439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3075,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R25" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,11 +3117,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,43 +3144,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3187,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R26" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,6 +3218,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3250,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725982</v>
+        <v>129725984</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456287</v>
+        <v>456330</v>
       </c>
       <c r="R27" t="n">
-        <v>6796072</v>
+        <v>6795990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725984</v>
+        <v>129725982</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456330</v>
+        <v>456287</v>
       </c>
       <c r="R28" t="n">
-        <v>6795990</v>
+        <v>6796072</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,54 +3567,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R30" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3674,45 +3664,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R31" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3753,6 +3752,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725940</v>
+        <v>129725988</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,42 +3782,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456159</v>
+        <v>456109</v>
       </c>
       <c r="R32" t="n">
-        <v>6796000</v>
+        <v>6796001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3887,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3911,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R33" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725960</v>
+        <v>129725940</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,34 +3976,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456343</v>
+        <v>456159</v>
       </c>
       <c r="R34" t="n">
-        <v>6796050</v>
+        <v>6796000</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725979</v>
+        <v>129725929</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456029</v>
+        <v>456209</v>
       </c>
       <c r="R35" t="n">
-        <v>6795946</v>
+        <v>6796011</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725929</v>
+        <v>129725941</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,34 +4178,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456209</v>
+        <v>456325</v>
       </c>
       <c r="R36" t="n">
-        <v>6796011</v>
+        <v>6796048</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,10 +4272,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725941</v>
+        <v>129725938</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,21 +4283,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,7 +4305,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4307,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456325</v>
+        <v>456346</v>
       </c>
       <c r="R37" t="n">
-        <v>6796048</v>
+        <v>6796076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,10 +4377,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725938</v>
+        <v>129725979</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4380,42 +4388,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456346</v>
+        <v>456029</v>
       </c>
       <c r="R38" t="n">
-        <v>6796076</v>
+        <v>6795946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129725920</v>
+        <v>129725921</v>
       </c>
       <c r="B47" t="n">
         <v>79700</v>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456344</v>
+        <v>456352</v>
       </c>
       <c r="R47" t="n">
-        <v>6795995</v>
+        <v>6796004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129725921</v>
+        <v>129725920</v>
       </c>
       <c r="B48" t="n">
         <v>79700</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456352</v>
+        <v>456344</v>
       </c>
       <c r="R48" t="n">
-        <v>6796004</v>
+        <v>6795995</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5481,37 +5481,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725983</v>
+        <v>129725958</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5519,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456325</v>
+        <v>456178</v>
       </c>
       <c r="R49" t="n">
-        <v>6796071</v>
+        <v>6795996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,11 +5561,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,10 +5588,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,34 +5599,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R50" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,12 +5664,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,54 +5694,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R51" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5773,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725993</v>
+        <v>129725915</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,37 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456038</v>
+        <v>456245</v>
       </c>
       <c r="R3" t="n">
-        <v>6795840</v>
+        <v>6795972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,18 +862,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725992</v>
+        <v>129725923</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456023</v>
+        <v>456270</v>
       </c>
       <c r="R4" t="n">
-        <v>6795818</v>
+        <v>6795982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,18 +959,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725996</v>
+        <v>129725993</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456173</v>
+        <v>456038</v>
       </c>
       <c r="R5" t="n">
-        <v>6795980</v>
+        <v>6795840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725915</v>
+        <v>129725992</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,34 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456245</v>
+        <v>456023</v>
       </c>
       <c r="R6" t="n">
-        <v>6795972</v>
+        <v>6795818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,12 +1165,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725923</v>
+        <v>129725996</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456270</v>
+        <v>456173</v>
       </c>
       <c r="R7" t="n">
-        <v>6795982</v>
+        <v>6795980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1271,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1301,54 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725948</v>
+        <v>129725917</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456265</v>
+        <v>456248</v>
       </c>
       <c r="R8" t="n">
-        <v>6796033</v>
+        <v>6796057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1408,45 +1398,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725917</v>
+        <v>129725948</v>
       </c>
       <c r="B9" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456248</v>
+        <v>456265</v>
       </c>
       <c r="R9" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1486,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,31 +1516,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1581,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,41 +1611,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725955</v>
+        <v>129725934</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456307</v>
+        <v>456358</v>
       </c>
       <c r="R11" t="n">
-        <v>6795993</v>
+        <v>6796007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1717,37 +1716,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725985</v>
+        <v>129725955</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456242</v>
+        <v>456307</v>
       </c>
       <c r="R12" t="n">
-        <v>6795974</v>
+        <v>6795993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,54 +1823,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725954</v>
+        <v>129725961</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456347</v>
+        <v>456325</v>
       </c>
       <c r="R13" t="n">
-        <v>6796030</v>
+        <v>6796001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1930,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129725961</v>
+        <v>129725918</v>
       </c>
       <c r="B14" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1965,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456325</v>
+        <v>456327</v>
       </c>
       <c r="R14" t="n">
-        <v>6796001</v>
+        <v>6796090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2114,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725918</v>
+        <v>129725916</v>
       </c>
       <c r="B16" t="n">
         <v>79700</v>
@@ -2159,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456327</v>
+        <v>456252</v>
       </c>
       <c r="R16" t="n">
-        <v>6796090</v>
+        <v>6795977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,45 +2211,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725916</v>
+        <v>129725954</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456252</v>
+        <v>456347</v>
       </c>
       <c r="R17" t="n">
-        <v>6795977</v>
+        <v>6796030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,6 +2299,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725984</v>
+        <v>129725982</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456330</v>
+        <v>456287</v>
       </c>
       <c r="R27" t="n">
-        <v>6795990</v>
+        <v>6796072</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725982</v>
+        <v>129725933</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,26 +3367,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3394,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456287</v>
+        <v>456029</v>
       </c>
       <c r="R28" t="n">
-        <v>6796072</v>
+        <v>6795960</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,18 +3437,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3462,10 +3461,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725933</v>
+        <v>129725984</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3473,31 +3472,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3505,10 +3499,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456029</v>
+        <v>456330</v>
       </c>
       <c r="R29" t="n">
-        <v>6795960</v>
+        <v>6795990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,12 +3537,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3567,45 +3567,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R30" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3655,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3664,54 +3674,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R31" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3753,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,21 +3782,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R32" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725960</v>
+        <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456343</v>
+        <v>456109</v>
       </c>
       <c r="R33" t="n">
-        <v>6796050</v>
+        <v>6796001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725938</v>
+        <v>129725979</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4283,42 +4283,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456346</v>
+        <v>456029</v>
       </c>
       <c r="R37" t="n">
-        <v>6796076</v>
+        <v>6795946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4377,10 +4369,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725979</v>
+        <v>129725938</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4388,34 +4380,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456029</v>
+        <v>456346</v>
       </c>
       <c r="R38" t="n">
-        <v>6795946</v>
+        <v>6796076</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5481,54 +5481,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R49" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,7 +5560,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5694,45 +5684,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725924</v>
+        <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456237</v>
+        <v>456178</v>
       </c>
       <c r="R51" t="n">
-        <v>6795975</v>
+        <v>6795996</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5772,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725915</v>
+        <v>129725992</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,34 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456245</v>
+        <v>456023</v>
       </c>
       <c r="R3" t="n">
-        <v>6795972</v>
+        <v>6795818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +865,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725923</v>
+        <v>129725996</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456270</v>
+        <v>456173</v>
       </c>
       <c r="R4" t="n">
-        <v>6795982</v>
+        <v>6795980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +971,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1118,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R6" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,18 +1180,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R7" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,18 +1277,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,26 +1516,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1586,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,40 +1610,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725934</v>
+        <v>129725955</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456358</v>
+        <v>456307</v>
       </c>
       <c r="R11" t="n">
-        <v>6796007</v>
+        <v>6795993</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1698,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1716,43 +1717,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725955</v>
+        <v>129725985</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456307</v>
+        <v>456242</v>
       </c>
       <c r="R12" t="n">
-        <v>6795993</v>
+        <v>6795974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2833,45 +2833,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R23" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,54 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R24" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3019,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129725995</v>
+        <v>129725987</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5008,19 +5008,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456299</v>
+        <v>456158</v>
       </c>
       <c r="R44" t="n">
-        <v>6795964</v>
+        <v>6795973</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,18 +5052,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5085,7 +5076,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129725987</v>
+        <v>129725995</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5114,16 +5105,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456158</v>
+        <v>456299</v>
       </c>
       <c r="R45" t="n">
-        <v>6795973</v>
+        <v>6795964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5158,12 +5152,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,37 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R3" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,18 +862,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R4" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,18 +959,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725915</v>
+        <v>129725992</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,34 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456245</v>
+        <v>456023</v>
       </c>
       <c r="R6" t="n">
-        <v>6795972</v>
+        <v>6795818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,12 +1165,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725923</v>
+        <v>129725996</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456270</v>
+        <v>456173</v>
       </c>
       <c r="R7" t="n">
-        <v>6795982</v>
+        <v>6795980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1271,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2629,45 +2629,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R21" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,6 +2717,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,54 +2736,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R22" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2815,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3567,54 +3567,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R30" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3674,45 +3664,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R31" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3753,6 +3752,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -5481,45 +5481,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725924</v>
+        <v>129725958</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456237</v>
+        <v>456178</v>
       </c>
       <c r="R49" t="n">
-        <v>6795975</v>
+        <v>6795996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5560,6 +5569,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5578,10 +5588,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725983</v>
+        <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5589,37 +5599,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456325</v>
+        <v>456237</v>
       </c>
       <c r="R50" t="n">
-        <v>6796071</v>
+        <v>6795975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5654,18 +5661,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,43 +5685,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725958</v>
+        <v>129725983</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5728,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456178</v>
+        <v>456325</v>
       </c>
       <c r="R51" t="n">
-        <v>6795996</v>
+        <v>6796071</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5764,6 +5759,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725915</v>
+        <v>129725992</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,34 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456245</v>
+        <v>456023</v>
       </c>
       <c r="R3" t="n">
-        <v>6795972</v>
+        <v>6795818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +865,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725923</v>
+        <v>129725996</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456270</v>
+        <v>456173</v>
       </c>
       <c r="R4" t="n">
-        <v>6795982</v>
+        <v>6795980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +971,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725993</v>
+        <v>129725915</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,37 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456038</v>
+        <v>456245</v>
       </c>
       <c r="R5" t="n">
-        <v>6795840</v>
+        <v>6795972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,18 +1074,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725992</v>
+        <v>129725923</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456023</v>
+        <v>456270</v>
       </c>
       <c r="R6" t="n">
-        <v>6795818</v>
+        <v>6795982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,18 +1171,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725996</v>
+        <v>129725993</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456173</v>
+        <v>456038</v>
       </c>
       <c r="R7" t="n">
-        <v>6795980</v>
+        <v>6795840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,31 +1516,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1581,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,41 +1611,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725955</v>
+        <v>129725934</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456307</v>
+        <v>456358</v>
       </c>
       <c r="R11" t="n">
-        <v>6795993</v>
+        <v>6796007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1717,37 +1716,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725985</v>
+        <v>129725955</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456242</v>
+        <v>456307</v>
       </c>
       <c r="R12" t="n">
-        <v>6795974</v>
+        <v>6795993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,45 +1823,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725961</v>
+        <v>129725954</v>
       </c>
       <c r="B13" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456325</v>
+        <v>456347</v>
       </c>
       <c r="R13" t="n">
-        <v>6796001</v>
+        <v>6796030</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1911,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2017,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725981</v>
+        <v>129725961</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456260</v>
+        <v>456325</v>
       </c>
       <c r="R15" t="n">
-        <v>6796058</v>
+        <v>6796001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,10 +2124,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725916</v>
+        <v>129725981</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2125,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2149,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456252</v>
+        <v>456260</v>
       </c>
       <c r="R16" t="n">
-        <v>6795977</v>
+        <v>6796058</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,54 +2221,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725954</v>
+        <v>129725916</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456347</v>
+        <v>456252</v>
       </c>
       <c r="R17" t="n">
-        <v>6796030</v>
+        <v>6795977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,7 +2300,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2629,54 +2629,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R21" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2708,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2736,45 +2726,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R22" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,6 +2814,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R23" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2940,45 +2930,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R24" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,6 +3018,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725982</v>
+        <v>129725984</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456287</v>
+        <v>456330</v>
       </c>
       <c r="R27" t="n">
-        <v>6796072</v>
+        <v>6795990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725933</v>
+        <v>129725982</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,31 +3367,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3399,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456029</v>
+        <v>456287</v>
       </c>
       <c r="R28" t="n">
-        <v>6795960</v>
+        <v>6796072</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,12 +3432,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3461,10 +3462,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725984</v>
+        <v>129725933</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3472,26 +3473,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3499,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456330</v>
+        <v>456029</v>
       </c>
       <c r="R29" t="n">
-        <v>6795990</v>
+        <v>6795960</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,18 +3543,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3567,45 +3567,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R30" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3655,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3664,54 +3674,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R31" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3753,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725929</v>
+        <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456209</v>
+        <v>456029</v>
       </c>
       <c r="R35" t="n">
-        <v>6796011</v>
+        <v>6795946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725941</v>
+        <v>129725929</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,42 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456325</v>
+        <v>456209</v>
       </c>
       <c r="R36" t="n">
-        <v>6796048</v>
+        <v>6796011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725979</v>
+        <v>129725941</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4283,34 +4275,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456029</v>
+        <v>456325</v>
       </c>
       <c r="R37" t="n">
-        <v>6795946</v>
+        <v>6796048</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129725987</v>
+        <v>129725995</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5008,16 +5008,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456158</v>
+        <v>456299</v>
       </c>
       <c r="R44" t="n">
-        <v>6795973</v>
+        <v>6795964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,12 +5055,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5076,7 +5085,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129725995</v>
+        <v>129725987</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5105,19 +5114,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456299</v>
+        <v>456158</v>
       </c>
       <c r="R45" t="n">
-        <v>6795964</v>
+        <v>6795973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5152,18 +5158,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5481,54 +5481,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R49" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,7 +5560,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5588,10 +5578,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,34 +5589,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R50" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5661,12 +5654,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5685,37 +5684,43 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725983</v>
+        <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5723,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456325</v>
+        <v>456178</v>
       </c>
       <c r="R51" t="n">
-        <v>6796071</v>
+        <v>6795996</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,11 +5764,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -4775,45 +4775,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725922</v>
+        <v>129725959</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456327</v>
+        <v>456177</v>
       </c>
       <c r="R42" t="n">
-        <v>6795987</v>
+        <v>6795973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,6 +4863,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4872,54 +4882,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725959</v>
+        <v>129725922</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456177</v>
+        <v>456327</v>
       </c>
       <c r="R43" t="n">
-        <v>6795973</v>
+        <v>6795987</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,7 +4961,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5481,45 +5481,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725924</v>
+        <v>129725958</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456237</v>
+        <v>456178</v>
       </c>
       <c r="R49" t="n">
-        <v>6795975</v>
+        <v>6795996</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5560,6 +5569,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5578,10 +5588,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725983</v>
+        <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5589,37 +5599,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456325</v>
+        <v>456237</v>
       </c>
       <c r="R50" t="n">
-        <v>6796071</v>
+        <v>6795975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5654,18 +5661,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,43 +5685,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725958</v>
+        <v>129725983</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5728,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456178</v>
+        <v>456325</v>
       </c>
       <c r="R51" t="n">
-        <v>6795996</v>
+        <v>6796071</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5764,6 +5759,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -2833,45 +2833,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R23" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,54 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R24" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3019,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3567,54 +3567,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R30" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3674,45 +3664,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R31" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3753,6 +3752,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725960</v>
+        <v>129725988</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,21 +3782,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456343</v>
+        <v>456109</v>
       </c>
       <c r="R32" t="n">
-        <v>6796050</v>
+        <v>6796001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R33" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725941</v>
+        <v>129725938</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,7 +4297,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456325</v>
+        <v>456346</v>
       </c>
       <c r="R37" t="n">
-        <v>6796048</v>
+        <v>6796076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,40 +4369,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725938</v>
+        <v>129725950</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4412,10 +4413,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456346</v>
+        <v>456341</v>
       </c>
       <c r="R38" t="n">
-        <v>6796076</v>
+        <v>6796057</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,6 +4457,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4474,41 +4476,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725950</v>
+        <v>129725941</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4518,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456341</v>
+        <v>456325</v>
       </c>
       <c r="R39" t="n">
-        <v>6796057</v>
+        <v>6796048</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,7 +4563,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4775,54 +4775,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725959</v>
+        <v>129725922</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456177</v>
+        <v>456327</v>
       </c>
       <c r="R42" t="n">
-        <v>6795973</v>
+        <v>6795987</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,7 +4854,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4882,45 +4872,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725922</v>
+        <v>129725959</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456327</v>
+        <v>456177</v>
       </c>
       <c r="R43" t="n">
-        <v>6795987</v>
+        <v>6795973</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,6 +4960,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,37 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R3" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,18 +862,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R4" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,18 +959,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725915</v>
+        <v>129725993</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +994,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456245</v>
+        <v>456038</v>
       </c>
       <c r="R5" t="n">
-        <v>6795972</v>
+        <v>6795840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,12 +1059,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725923</v>
+        <v>129725992</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456270</v>
+        <v>456023</v>
       </c>
       <c r="R6" t="n">
-        <v>6795982</v>
+        <v>6795818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,12 +1165,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725993</v>
+        <v>129725996</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456038</v>
+        <v>456173</v>
       </c>
       <c r="R7" t="n">
-        <v>6795840</v>
+        <v>6795980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,7 +1304,7 @@
         <v>129725917</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,37 +1505,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725955</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456307</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6795993</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,11 +1585,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,31 +1623,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1654,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R11" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,12 +1688,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1716,41 +1718,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725955</v>
+        <v>129725934</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1760,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456307</v>
+        <v>456358</v>
       </c>
       <c r="R12" t="n">
-        <v>6795993</v>
+        <v>6796007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1805,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1823,54 +1823,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129725954</v>
+        <v>129725961</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456347</v>
+        <v>456325</v>
       </c>
       <c r="R13" t="n">
-        <v>6796030</v>
+        <v>6796001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1933,7 +1923,7 @@
         <v>129725918</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2027,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725961</v>
+        <v>129725981</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456325</v>
+        <v>456260</v>
       </c>
       <c r="R15" t="n">
-        <v>6796001</v>
+        <v>6796058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725981</v>
+        <v>129725916</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,21 +2125,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456260</v>
+        <v>456252</v>
       </c>
       <c r="R16" t="n">
-        <v>6796058</v>
+        <v>6795977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,45 +2211,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725916</v>
+        <v>129725954</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456252</v>
+        <v>456347</v>
       </c>
       <c r="R17" t="n">
-        <v>6795977</v>
+        <v>6796030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,6 +2299,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>129725930</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R23" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2940,45 +2930,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R24" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,6 +3018,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,43 +3037,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B25" t="n">
-        <v>8439</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3081,10 +3075,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R25" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,6 +3111,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3144,37 +3143,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>8439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3182,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R26" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,11 +3223,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3253,7 +3253,7 @@
         <v>129725984</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>129725982</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>129725933</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,21 +3782,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R32" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725960</v>
+        <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456343</v>
+        <v>456109</v>
       </c>
       <c r="R33" t="n">
-        <v>6796050</v>
+        <v>6796001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
         <v>129725940</v>
       </c>
       <c r="B34" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>129725929</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725938</v>
+        <v>129725941</v>
       </c>
       <c r="B37" t="n">
-        <v>57896</v>
+        <v>57734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4297,7 +4297,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456346</v>
+        <v>456325</v>
       </c>
       <c r="R37" t="n">
-        <v>6796076</v>
+        <v>6796048</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,41 +4369,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725950</v>
+        <v>129725938</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4413,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456341</v>
+        <v>456346</v>
       </c>
       <c r="R38" t="n">
-        <v>6796057</v>
+        <v>6796076</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,7 +4456,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4476,40 +4474,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725941</v>
+        <v>129725950</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4519,10 +4518,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456325</v>
+        <v>456341</v>
       </c>
       <c r="R39" t="n">
-        <v>6796048</v>
+        <v>6796057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,6 +4562,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>129725975</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129725928</v>
       </c>
       <c r="B41" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4775,45 +4775,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725922</v>
+        <v>129725959</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456327</v>
+        <v>456177</v>
       </c>
       <c r="R42" t="n">
-        <v>6795987</v>
+        <v>6795973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,6 +4863,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4872,54 +4882,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725959</v>
+        <v>129725922</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456177</v>
+        <v>456327</v>
       </c>
       <c r="R43" t="n">
-        <v>6795973</v>
+        <v>6795987</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,7 +4961,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>129725995</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>129725987</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>129725942</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>129725921</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129725920</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>129725983</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>129725939</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>129725986</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -2833,45 +2833,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R23" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,54 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R24" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3019,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -5481,54 +5481,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725958</v>
+        <v>129725924</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456178</v>
+        <v>456237</v>
       </c>
       <c r="R49" t="n">
-        <v>6795996</v>
+        <v>6795975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5569,7 +5560,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5588,10 +5578,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B50" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,34 +5589,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R50" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5661,12 +5654,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5685,37 +5684,43 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725983</v>
+        <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5723,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456325</v>
+        <v>456178</v>
       </c>
       <c r="R51" t="n">
-        <v>6796071</v>
+        <v>6795996</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,11 +5764,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725915</v>
+        <v>129725993</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,34 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456245</v>
+        <v>456038</v>
       </c>
       <c r="R3" t="n">
-        <v>6795972</v>
+        <v>6795840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +865,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725923</v>
+        <v>129725992</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456270</v>
+        <v>456023</v>
       </c>
       <c r="R4" t="n">
-        <v>6795982</v>
+        <v>6795818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +971,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725993</v>
+        <v>129725996</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456038</v>
+        <v>456173</v>
       </c>
       <c r="R5" t="n">
-        <v>6795840</v>
+        <v>6795980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1118,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R6" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,18 +1180,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R7" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,18 +1277,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1301,45 +1301,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725917</v>
+        <v>129725948</v>
       </c>
       <c r="B8" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456248</v>
+        <v>456265</v>
       </c>
       <c r="R8" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,54 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725948</v>
+        <v>129725917</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456265</v>
+        <v>456248</v>
       </c>
       <c r="R9" t="n">
-        <v>6796033</v>
+        <v>6796057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,7 +1487,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,43 +1505,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725955</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1549,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456307</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6795993</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,6 +1579,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,37 +1611,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725985</v>
+        <v>129725955</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1650,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456242</v>
+        <v>456307</v>
       </c>
       <c r="R11" t="n">
-        <v>6795974</v>
+        <v>6795993</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,11 +1691,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,7 +1721,7 @@
         <v>129725934</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>129725961</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129725918</v>
+        <v>129725981</v>
       </c>
       <c r="B14" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456327</v>
+        <v>456260</v>
       </c>
       <c r="R14" t="n">
-        <v>6796090</v>
+        <v>6796058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725981</v>
+        <v>129725918</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456260</v>
+        <v>456327</v>
       </c>
       <c r="R15" t="n">
-        <v>6796058</v>
+        <v>6796090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,7 +2117,7 @@
         <v>129725916</v>
       </c>
       <c r="B16" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>129725954</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>129725956</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,45 +2425,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725930</v>
+        <v>129725951</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456248</v>
+        <v>456335</v>
       </c>
       <c r="R19" t="n">
-        <v>6795998</v>
+        <v>6796044</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,6 +2513,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2522,54 +2532,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129725951</v>
+        <v>129725930</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456335</v>
+        <v>456248</v>
       </c>
       <c r="R20" t="n">
-        <v>6796044</v>
+        <v>6795998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,7 +2611,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>129725953</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,37 +3037,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>8440</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3075,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R25" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,11 +3117,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,43 +3144,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>8439</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3187,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R26" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,6 +3218,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3253,7 +3253,7 @@
         <v>129725984</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>129725982</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>129725933</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>129725957</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>129725960</v>
       </c>
       <c r="B32" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129725940</v>
       </c>
       <c r="B34" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>129725929</v>
       </c>
       <c r="B36" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>129725941</v>
       </c>
       <c r="B37" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>129725938</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>129725950</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129725975</v>
+        <v>129725928</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456012</v>
+        <v>456207</v>
       </c>
       <c r="R40" t="n">
-        <v>6795798</v>
+        <v>6796000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129725928</v>
+        <v>129725975</v>
       </c>
       <c r="B41" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456207</v>
+        <v>456012</v>
       </c>
       <c r="R41" t="n">
-        <v>6796000</v>
+        <v>6795798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4775,54 +4775,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725959</v>
+        <v>129725922</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456177</v>
+        <v>456327</v>
       </c>
       <c r="R42" t="n">
-        <v>6795973</v>
+        <v>6795987</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,7 +4854,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4882,45 +4872,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725922</v>
+        <v>129725959</v>
       </c>
       <c r="B43" t="n">
-        <v>79703</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456327</v>
+        <v>456177</v>
       </c>
       <c r="R43" t="n">
-        <v>6795987</v>
+        <v>6795973</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,6 +4960,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129725995</v>
+        <v>129725942</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4990,26 +4990,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5017,10 +5022,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456299</v>
+        <v>456107</v>
       </c>
       <c r="R44" t="n">
-        <v>6795964</v>
+        <v>6795991</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,18 +5060,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5085,10 +5084,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129725987</v>
+        <v>129725995</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,16 +5113,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456158</v>
+        <v>456299</v>
       </c>
       <c r="R45" t="n">
-        <v>6795973</v>
+        <v>6795964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5158,12 +5160,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5182,10 +5190,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129725942</v>
+        <v>129725987</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5193,42 +5201,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456107</v>
+        <v>456158</v>
       </c>
       <c r="R46" t="n">
-        <v>6795991</v>
+        <v>6795973</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
         <v>129725921</v>
       </c>
       <c r="B47" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129725920</v>
       </c>
       <c r="B48" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B49" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,34 +5492,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R49" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5554,12 +5557,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5578,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725983</v>
+        <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5589,37 +5598,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456325</v>
+        <v>456237</v>
       </c>
       <c r="R50" t="n">
-        <v>6796071</v>
+        <v>6795975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5654,18 +5660,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>129725958</v>
       </c>
       <c r="B51" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>129725939</v>
       </c>
       <c r="B52" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>129725986</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,26 +1516,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1586,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1718,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,31 +1728,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1761,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R12" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,12 +1793,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R23" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2940,45 +2930,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R24" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,6 +3018,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,43 +3037,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B25" t="n">
-        <v>8440</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3081,10 +3075,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R25" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,6 +3111,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3144,37 +3143,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>8440</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3182,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R26" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3218,11 +3223,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725960</v>
+        <v>129725940</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,34 +3782,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456343</v>
+        <v>456159</v>
       </c>
       <c r="R32" t="n">
-        <v>6796050</v>
+        <v>6796000</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725988</v>
+        <v>129725960</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3887,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456109</v>
+        <v>456343</v>
       </c>
       <c r="R33" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3965,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725940</v>
+        <v>129725988</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,42 +3984,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456159</v>
+        <v>456109</v>
       </c>
       <c r="R34" t="n">
-        <v>6796000</v>
+        <v>6796001</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,31 +1516,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R10" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1581,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1717,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,26 +1729,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1755,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R12" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,18 +1799,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2833,45 +2833,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R23" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,54 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R24" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3019,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,37 +3037,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129725973</v>
+        <v>129726002</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>8440</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3075,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456117</v>
+        <v>456047</v>
       </c>
       <c r="R25" t="n">
-        <v>6795876</v>
+        <v>6795976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,11 +3117,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,43 +3144,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129726002</v>
+        <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>8440</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3187,10 +3182,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456047</v>
+        <v>456117</v>
       </c>
       <c r="R26" t="n">
-        <v>6795976</v>
+        <v>6795876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,6 +3218,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med Garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725979</v>
+        <v>129725938</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>57898</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,34 +4081,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456029</v>
+        <v>456346</v>
       </c>
       <c r="R35" t="n">
-        <v>6795946</v>
+        <v>6796076</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,45 +4175,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725929</v>
+        <v>129725950</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456209</v>
+        <v>456341</v>
       </c>
       <c r="R36" t="n">
-        <v>6796011</v>
+        <v>6796057</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4246,6 +4263,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4264,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725941</v>
+        <v>129725979</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,42 +4293,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456325</v>
+        <v>456029</v>
       </c>
       <c r="R37" t="n">
-        <v>6796048</v>
+        <v>6795946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,10 +4379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725938</v>
+        <v>129725929</v>
       </c>
       <c r="B38" t="n">
-        <v>57898</v>
+        <v>79706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4380,42 +4390,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456346</v>
+        <v>456209</v>
       </c>
       <c r="R38" t="n">
-        <v>6796076</v>
+        <v>6796011</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,41 +4476,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725950</v>
+        <v>129725941</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4518,10 +4519,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456341</v>
+        <v>456325</v>
       </c>
       <c r="R39" t="n">
-        <v>6796057</v>
+        <v>6796048</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,7 +4563,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725993</v>
+        <v>129725915</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,37 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456038</v>
+        <v>456245</v>
       </c>
       <c r="R3" t="n">
-        <v>6795840</v>
+        <v>6795972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,18 +862,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725992</v>
+        <v>129725923</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +897,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456023</v>
+        <v>456270</v>
       </c>
       <c r="R4" t="n">
-        <v>6795818</v>
+        <v>6795982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,18 +959,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129725996</v>
+        <v>129725993</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456173</v>
+        <v>456038</v>
       </c>
       <c r="R5" t="n">
-        <v>6795980</v>
+        <v>6795840</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725915</v>
+        <v>129725992</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,34 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456245</v>
+        <v>456023</v>
       </c>
       <c r="R6" t="n">
-        <v>6795972</v>
+        <v>6795818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,12 +1165,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725923</v>
+        <v>129725996</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,34 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456270</v>
+        <v>456173</v>
       </c>
       <c r="R7" t="n">
-        <v>6795982</v>
+        <v>6795980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1271,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1301,54 +1301,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129725948</v>
+        <v>129725917</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456265</v>
+        <v>456248</v>
       </c>
       <c r="R8" t="n">
-        <v>6796033</v>
+        <v>6796057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1408,45 +1398,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129725917</v>
+        <v>129725948</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456248</v>
+        <v>456265</v>
       </c>
       <c r="R9" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1486,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>129725985</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,41 +1611,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725955</v>
+        <v>129725934</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1655,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456307</v>
+        <v>456358</v>
       </c>
       <c r="R11" t="n">
-        <v>6795993</v>
+        <v>6796007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,7 +1698,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1718,40 +1716,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129725934</v>
+        <v>129725955</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1761,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456358</v>
+        <v>456307</v>
       </c>
       <c r="R12" t="n">
-        <v>6796007</v>
+        <v>6795993</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,6 +1804,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>129725961</v>
       </c>
       <c r="B13" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129725981</v>
+        <v>129725918</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456260</v>
+        <v>456327</v>
       </c>
       <c r="R14" t="n">
-        <v>6796058</v>
+        <v>6796090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725918</v>
+        <v>129725981</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456327</v>
+        <v>456260</v>
       </c>
       <c r="R15" t="n">
-        <v>6796090</v>
+        <v>6796058</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,7 +2117,7 @@
         <v>129725916</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,54 +2425,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129725951</v>
+        <v>129725930</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456335</v>
+        <v>456248</v>
       </c>
       <c r="R19" t="n">
-        <v>6796044</v>
+        <v>6795998</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,7 +2504,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2532,45 +2522,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129725930</v>
+        <v>129725951</v>
       </c>
       <c r="B20" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456248</v>
+        <v>456335</v>
       </c>
       <c r="R20" t="n">
-        <v>6795998</v>
+        <v>6796044</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2611,6 +2610,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2629,45 +2629,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R21" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,6 +2717,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2726,54 +2736,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R22" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2815,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R23" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2940,45 +2930,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R24" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,6 +3018,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>129725984</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>129725982</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,45 +3567,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R30" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,6 +3655,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3664,54 +3674,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R31" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3752,7 +3753,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725940</v>
+        <v>129725960</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,42 +3782,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456159</v>
+        <v>456343</v>
       </c>
       <c r="R32" t="n">
-        <v>6796000</v>
+        <v>6796050</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,10 +3868,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725960</v>
+        <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3887,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3911,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456343</v>
+        <v>456109</v>
       </c>
       <c r="R33" t="n">
-        <v>6796050</v>
+        <v>6796001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3965,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725988</v>
+        <v>129725940</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,34 +3976,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456109</v>
+        <v>456159</v>
       </c>
       <c r="R34" t="n">
-        <v>6796001</v>
+        <v>6796000</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725938</v>
+        <v>129725941</v>
       </c>
       <c r="B35" t="n">
-        <v>57898</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456346</v>
+        <v>456325</v>
       </c>
       <c r="R35" t="n">
-        <v>6796076</v>
+        <v>6796048</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,41 +4175,40 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725950</v>
+        <v>129725938</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>57898</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4219,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456341</v>
+        <v>456346</v>
       </c>
       <c r="R36" t="n">
-        <v>6796057</v>
+        <v>6796076</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4263,7 +4262,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4282,45 +4280,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725979</v>
+        <v>129725950</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456029</v>
+        <v>456341</v>
       </c>
       <c r="R37" t="n">
-        <v>6795946</v>
+        <v>6796057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,6 +4368,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4379,10 +4387,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725929</v>
+        <v>129725979</v>
       </c>
       <c r="B38" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4390,21 +4398,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4414,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456209</v>
+        <v>456029</v>
       </c>
       <c r="R38" t="n">
-        <v>6796011</v>
+        <v>6795946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4476,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725941</v>
+        <v>129725929</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4487,42 +4495,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456325</v>
+        <v>456209</v>
       </c>
       <c r="R39" t="n">
-        <v>6796048</v>
+        <v>6796011</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
         <v>129725928</v>
       </c>
       <c r="B40" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>129725975</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>129725922</v>
       </c>
       <c r="B42" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129725942</v>
+        <v>129725995</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4990,31 +4990,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5022,10 +5017,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456107</v>
+        <v>456299</v>
       </c>
       <c r="R44" t="n">
-        <v>6795991</v>
+        <v>6795964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5060,12 +5055,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5084,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129725995</v>
+        <v>129725987</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5113,19 +5114,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456299</v>
+        <v>456158</v>
       </c>
       <c r="R45" t="n">
-        <v>6795964</v>
+        <v>6795973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5160,18 +5158,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5190,10 +5182,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129725987</v>
+        <v>129725942</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5201,34 +5193,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456158</v>
+        <v>456107</v>
       </c>
       <c r="R46" t="n">
-        <v>6795973</v>
+        <v>6795991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
         <v>129725921</v>
       </c>
       <c r="B47" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129725920</v>
       </c>
       <c r="B48" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725983</v>
+        <v>129725924</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,37 +5492,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456325</v>
+        <v>456237</v>
       </c>
       <c r="R49" t="n">
-        <v>6796071</v>
+        <v>6795975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5557,18 +5554,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5587,10 +5578,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B50" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,34 +5589,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R50" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5660,12 +5654,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>129725986</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -2833,45 +2833,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R23" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2930,54 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R24" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3019,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129725915</v>
+        <v>129725996</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,34 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456245</v>
+        <v>456173</v>
       </c>
       <c r="R3" t="n">
-        <v>6795972</v>
+        <v>6795980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,12 +865,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129725923</v>
+        <v>129725992</v>
       </c>
       <c r="B4" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,34 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456270</v>
+        <v>456023</v>
       </c>
       <c r="R4" t="n">
-        <v>6795982</v>
+        <v>6795818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +971,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,7 +1004,7 @@
         <v>129725993</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129725992</v>
+        <v>129725915</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,37 +1118,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456023</v>
+        <v>456245</v>
       </c>
       <c r="R6" t="n">
-        <v>6795818</v>
+        <v>6795972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,18 +1180,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granar och tallar är rikligt(!) draperade med garnlav, inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129725996</v>
+        <v>129725923</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,37 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456173</v>
+        <v>456270</v>
       </c>
       <c r="R7" t="n">
-        <v>6795980</v>
+        <v>6795982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,18 +1277,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>129725917</v>
       </c>
       <c r="B8" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129725985</v>
+        <v>129725934</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,26 +1516,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1543,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456242</v>
+        <v>456358</v>
       </c>
       <c r="R10" t="n">
-        <v>6795974</v>
+        <v>6796007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1586,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129725934</v>
+        <v>129725985</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,31 +1621,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1654,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456358</v>
+        <v>456242</v>
       </c>
       <c r="R11" t="n">
-        <v>6796007</v>
+        <v>6795974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,12 +1686,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>129725961</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>129725918</v>
       </c>
       <c r="B14" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129725981</v>
+        <v>129725916</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456260</v>
+        <v>456252</v>
       </c>
       <c r="R15" t="n">
-        <v>6796058</v>
+        <v>6795977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,45 +2114,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129725916</v>
+        <v>129725954</v>
       </c>
       <c r="B16" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456252</v>
+        <v>456347</v>
       </c>
       <c r="R16" t="n">
-        <v>6795977</v>
+        <v>6796030</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,6 +2202,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2211,54 +2221,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129725954</v>
+        <v>129725981</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456347</v>
+        <v>456260</v>
       </c>
       <c r="R17" t="n">
-        <v>6796030</v>
+        <v>6796058</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2299,7 +2300,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>129725930</v>
       </c>
       <c r="B19" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,54 +2629,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129725953</v>
+        <v>129725919</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456343</v>
+        <v>456333</v>
       </c>
       <c r="R21" t="n">
-        <v>6796032</v>
+        <v>6796026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2708,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2736,45 +2726,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129725919</v>
+        <v>129725953</v>
       </c>
       <c r="B22" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456333</v>
+        <v>456343</v>
       </c>
       <c r="R22" t="n">
-        <v>6796026</v>
+        <v>6796032</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,6 +2814,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2833,54 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129725952</v>
+        <v>129725994</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456328</v>
+        <v>456022</v>
       </c>
       <c r="R23" t="n">
-        <v>6796020</v>
+        <v>6795956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2940,45 +2930,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129725994</v>
+        <v>129725952</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456022</v>
+        <v>456328</v>
       </c>
       <c r="R24" t="n">
-        <v>6795956</v>
+        <v>6796020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3019,6 +3018,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>129725973</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725984</v>
+        <v>129725982</v>
       </c>
       <c r="B27" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456330</v>
+        <v>456287</v>
       </c>
       <c r="R27" t="n">
-        <v>6795990</v>
+        <v>6796072</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725982</v>
+        <v>129725984</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456287</v>
+        <v>456330</v>
       </c>
       <c r="R28" t="n">
-        <v>6796072</v>
+        <v>6795990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,54 +3567,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725957</v>
+        <v>129725997</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456253</v>
+        <v>456179</v>
       </c>
       <c r="R30" t="n">
-        <v>6795980</v>
+        <v>6795973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3655,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3674,45 +3664,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725997</v>
+        <v>129725957</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456179</v>
+        <v>456253</v>
       </c>
       <c r="R31" t="n">
-        <v>6795973</v>
+        <v>6795980</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3753,6 +3752,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>129725960</v>
       </c>
       <c r="B32" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129725988</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725941</v>
+        <v>129725979</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,42 +4081,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456325</v>
+        <v>456029</v>
       </c>
       <c r="R35" t="n">
-        <v>6796048</v>
+        <v>6795946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725938</v>
+        <v>129725929</v>
       </c>
       <c r="B36" t="n">
-        <v>57898</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4186,42 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456346</v>
+        <v>456209</v>
       </c>
       <c r="R36" t="n">
-        <v>6796076</v>
+        <v>6796011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,41 +4264,40 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725950</v>
+        <v>129725941</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4324,10 +4307,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456341</v>
+        <v>456325</v>
       </c>
       <c r="R37" t="n">
-        <v>6796057</v>
+        <v>6796048</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4351,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4387,10 +4369,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725979</v>
+        <v>129725938</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>57899</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4398,34 +4380,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456029</v>
+        <v>456346</v>
       </c>
       <c r="R38" t="n">
-        <v>6795946</v>
+        <v>6796076</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4484,45 +4474,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725929</v>
+        <v>129725950</v>
       </c>
       <c r="B39" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456209</v>
+        <v>456341</v>
       </c>
       <c r="R39" t="n">
-        <v>6796011</v>
+        <v>6796057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,6 +4562,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129725928</v>
+        <v>129725975</v>
       </c>
       <c r="B40" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4592,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456207</v>
+        <v>456012</v>
       </c>
       <c r="R40" t="n">
-        <v>6796000</v>
+        <v>6795798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129725975</v>
+        <v>129725928</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456012</v>
+        <v>456207</v>
       </c>
       <c r="R41" t="n">
-        <v>6795798</v>
+        <v>6796000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4778,7 +4778,7 @@
         <v>129725922</v>
       </c>
       <c r="B42" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4979,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129725995</v>
+        <v>129725942</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4990,26 +4990,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5017,10 +5022,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456299</v>
+        <v>456107</v>
       </c>
       <c r="R44" t="n">
-        <v>6795964</v>
+        <v>6795991</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,18 +5060,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5088,7 +5087,7 @@
         <v>129725987</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5182,10 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129725942</v>
+        <v>129725995</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5193,31 +5192,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5225,10 +5219,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456107</v>
+        <v>456299</v>
       </c>
       <c r="R46" t="n">
-        <v>6795991</v>
+        <v>6795964</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5263,12 +5257,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>129725921</v>
       </c>
       <c r="B47" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129725920</v>
       </c>
       <c r="B48" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725924</v>
+        <v>129725983</v>
       </c>
       <c r="B49" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,34 +5492,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456237</v>
+        <v>456325</v>
       </c>
       <c r="R49" t="n">
-        <v>6795975</v>
+        <v>6796071</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5554,12 +5557,18 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5578,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725983</v>
+        <v>129725924</v>
       </c>
       <c r="B50" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5589,37 +5598,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456325</v>
+        <v>456237</v>
       </c>
       <c r="R50" t="n">
-        <v>6796071</v>
+        <v>6795975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5654,18 +5660,12 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>129725986</v>
       </c>
       <c r="B53" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3092,45 +3092,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129725960</v>
+        <v>135141614</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Manmyren, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>456343</v>
+        <v>455938</v>
       </c>
       <c r="R26" t="n">
-        <v>6796050</v>
+        <v>6795927</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3157,12 +3160,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3171,25 +3174,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129725961</v>
+        <v>129725960</v>
       </c>
       <c r="B27" t="n">
         <v>79084</v>
@@ -3224,10 +3228,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>456325</v>
+        <v>456343</v>
       </c>
       <c r="R27" t="n">
-        <v>6796001</v>
+        <v>6796050</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,10 +3290,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129725913</v>
+        <v>129725961</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,21 +3301,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3321,10 +3325,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>456099</v>
+        <v>456325</v>
       </c>
       <c r="R28" t="n">
-        <v>6795828</v>
+        <v>6796001</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,7 +3387,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129725915</v>
+        <v>129725913</v>
       </c>
       <c r="B29" t="n">
         <v>79946</v>
@@ -3418,10 +3422,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>456245</v>
+        <v>456099</v>
       </c>
       <c r="R29" t="n">
-        <v>6795972</v>
+        <v>6795828</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3480,7 +3484,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129725916</v>
+        <v>129725915</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -3515,10 +3519,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>456252</v>
+        <v>456245</v>
       </c>
       <c r="R30" t="n">
-        <v>6795977</v>
+        <v>6795972</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3577,7 +3581,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129725917</v>
+        <v>129725916</v>
       </c>
       <c r="B31" t="n">
         <v>79946</v>
@@ -3612,10 +3616,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456248</v>
+        <v>456252</v>
       </c>
       <c r="R31" t="n">
-        <v>6796057</v>
+        <v>6795977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3674,7 +3678,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129725918</v>
+        <v>129725917</v>
       </c>
       <c r="B32" t="n">
         <v>79946</v>
@@ -3709,10 +3713,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456327</v>
+        <v>456248</v>
       </c>
       <c r="R32" t="n">
-        <v>6796090</v>
+        <v>6796057</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3771,7 +3775,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129725919</v>
+        <v>129725918</v>
       </c>
       <c r="B33" t="n">
         <v>79946</v>
@@ -3806,10 +3810,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456333</v>
+        <v>456327</v>
       </c>
       <c r="R33" t="n">
-        <v>6796026</v>
+        <v>6796090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3868,7 +3872,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129725920</v>
+        <v>129725919</v>
       </c>
       <c r="B34" t="n">
         <v>79946</v>
@@ -3903,10 +3907,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>456344</v>
+        <v>456333</v>
       </c>
       <c r="R34" t="n">
-        <v>6795995</v>
+        <v>6796026</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3965,7 +3969,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129725921</v>
+        <v>129725920</v>
       </c>
       <c r="B35" t="n">
         <v>79946</v>
@@ -4000,10 +4004,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>456352</v>
+        <v>456344</v>
       </c>
       <c r="R35" t="n">
-        <v>6796004</v>
+        <v>6795995</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4062,7 +4066,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129725922</v>
+        <v>129725921</v>
       </c>
       <c r="B36" t="n">
         <v>79946</v>
@@ -4097,10 +4101,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>456327</v>
+        <v>456352</v>
       </c>
       <c r="R36" t="n">
-        <v>6795987</v>
+        <v>6796004</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4159,7 +4163,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129725923</v>
+        <v>129725922</v>
       </c>
       <c r="B37" t="n">
         <v>79946</v>
@@ -4194,10 +4198,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456270</v>
+        <v>456327</v>
       </c>
       <c r="R37" t="n">
-        <v>6795982</v>
+        <v>6795987</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4256,7 +4260,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129725924</v>
+        <v>129725923</v>
       </c>
       <c r="B38" t="n">
         <v>79946</v>
@@ -4291,10 +4295,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456237</v>
+        <v>456270</v>
       </c>
       <c r="R38" t="n">
-        <v>6795975</v>
+        <v>6795982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4353,7 +4357,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129725928</v>
+        <v>129725924</v>
       </c>
       <c r="B39" t="n">
         <v>79946</v>
@@ -4388,10 +4392,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>456207</v>
+        <v>456237</v>
       </c>
       <c r="R39" t="n">
-        <v>6796000</v>
+        <v>6795975</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4450,7 +4454,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129725929</v>
+        <v>129725928</v>
       </c>
       <c r="B40" t="n">
         <v>79946</v>
@@ -4485,10 +4489,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>456209</v>
+        <v>456207</v>
       </c>
       <c r="R40" t="n">
-        <v>6796011</v>
+        <v>6796000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4547,7 +4551,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129725930</v>
+        <v>129725929</v>
       </c>
       <c r="B41" t="n">
         <v>79946</v>
@@ -4582,10 +4586,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>456248</v>
+        <v>456209</v>
       </c>
       <c r="R41" t="n">
-        <v>6795998</v>
+        <v>6796011</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4644,53 +4648,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129725939</v>
+        <v>129725930</v>
       </c>
       <c r="B42" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456003</v>
+        <v>456248</v>
       </c>
       <c r="R42" t="n">
-        <v>6795938</v>
+        <v>6795998</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4749,7 +4745,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129725940</v>
+        <v>129725939</v>
       </c>
       <c r="B43" t="n">
         <v>57950</v>
@@ -4782,7 +4778,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4792,10 +4788,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>456159</v>
+        <v>456003</v>
       </c>
       <c r="R43" t="n">
-        <v>6796000</v>
+        <v>6795938</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4854,7 +4850,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129725941</v>
+        <v>129725940</v>
       </c>
       <c r="B44" t="n">
         <v>57950</v>
@@ -4887,7 +4883,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4897,10 +4893,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456325</v>
+        <v>456159</v>
       </c>
       <c r="R44" t="n">
-        <v>6796048</v>
+        <v>6796000</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4959,7 +4955,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129725942</v>
+        <v>129725941</v>
       </c>
       <c r="B45" t="n">
         <v>57950</v>
@@ -4992,7 +4988,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5002,10 +4998,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>456107</v>
+        <v>456325</v>
       </c>
       <c r="R45" t="n">
-        <v>6795991</v>
+        <v>6796048</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5064,27 +5060,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120805255</v>
+        <v>129725942</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5100,24 +5096,20 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slätbergsbäcken, Hykjeberg, Dlr</t>
+          <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>456148</v>
+        <v>456107</v>
       </c>
       <c r="R46" t="n">
-        <v>6795984</v>
+        <v>6795991</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5141,12 +5133,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,19 +5153,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129725932</v>
+        <v>120805255</v>
       </c>
       <c r="B47" t="n">
         <v>57953</v>
@@ -5209,20 +5201,24 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Manmyren, Dlr</t>
+          <t>Slätbergsbäcken, Hykjeberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>456025</v>
+        <v>456148</v>
       </c>
       <c r="R47" t="n">
-        <v>6795921</v>
+        <v>6795984</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5246,12 +5242,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5266,19 +5262,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129725933</v>
+        <v>129725932</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -5321,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>456029</v>
+        <v>456025</v>
       </c>
       <c r="R48" t="n">
-        <v>6795960</v>
+        <v>6795921</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5383,7 +5379,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129725934</v>
+        <v>129725933</v>
       </c>
       <c r="B49" t="n">
         <v>57953</v>
@@ -5426,10 +5422,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>456358</v>
+        <v>456029</v>
       </c>
       <c r="R49" t="n">
-        <v>6796007</v>
+        <v>6795960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5488,7 +5484,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129725935</v>
+        <v>129725934</v>
       </c>
       <c r="B50" t="n">
         <v>57953</v>
@@ -5531,10 +5527,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>456156</v>
+        <v>456358</v>
       </c>
       <c r="R50" t="n">
-        <v>6795965</v>
+        <v>6796007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5589,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129725936</v>
+        <v>129725935</v>
       </c>
       <c r="B51" t="n">
         <v>57953</v>
@@ -5636,10 +5632,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456143</v>
+        <v>456156</v>
       </c>
       <c r="R51" t="n">
-        <v>6795961</v>
+        <v>6795965</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5698,32 +5694,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134380916</v>
+        <v>129725936</v>
       </c>
       <c r="B52" t="n">
-        <v>58461</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5731,20 +5727,20 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Hykjeberg, Dlr</t>
+          <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456048</v>
+        <v>456143</v>
       </c>
       <c r="R52" t="n">
-        <v>6795965</v>
+        <v>6795961</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5771,12 +5767,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5791,44 +5787,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129725938</v>
+        <v>134380916</v>
       </c>
       <c r="B53" t="n">
-        <v>58114</v>
+        <v>58461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5836,20 +5832,20 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Manmyren, Dlr</t>
+          <t>Manmyrbäck, Hykjeberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>456346</v>
+        <v>456048</v>
       </c>
       <c r="R53" t="n">
-        <v>6796076</v>
+        <v>6795965</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,12 +5872,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5896,53 +5892,52 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129725948</v>
+        <v>129725938</v>
       </c>
       <c r="B54" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5952,10 +5947,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>456265</v>
+        <v>456346</v>
       </c>
       <c r="R54" t="n">
-        <v>6796033</v>
+        <v>6796076</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5996,7 +5991,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6015,7 +6009,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129725950</v>
+        <v>129725948</v>
       </c>
       <c r="B55" t="n">
         <v>8455</v>
@@ -6059,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>456341</v>
+        <v>456265</v>
       </c>
       <c r="R55" t="n">
-        <v>6796057</v>
+        <v>6796033</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6122,7 +6116,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129725951</v>
+        <v>129725950</v>
       </c>
       <c r="B56" t="n">
         <v>8455</v>
@@ -6166,10 +6160,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>456335</v>
+        <v>456341</v>
       </c>
       <c r="R56" t="n">
-        <v>6796044</v>
+        <v>6796057</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6229,7 +6223,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129725952</v>
+        <v>129725951</v>
       </c>
       <c r="B57" t="n">
         <v>8455</v>
@@ -6273,10 +6267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>456328</v>
+        <v>456335</v>
       </c>
       <c r="R57" t="n">
-        <v>6796020</v>
+        <v>6796044</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6336,7 +6330,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129725953</v>
+        <v>129725952</v>
       </c>
       <c r="B58" t="n">
         <v>8455</v>
@@ -6380,10 +6374,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>456343</v>
+        <v>456328</v>
       </c>
       <c r="R58" t="n">
-        <v>6796032</v>
+        <v>6796020</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6443,7 +6437,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129725954</v>
+        <v>129725953</v>
       </c>
       <c r="B59" t="n">
         <v>8455</v>
@@ -6487,10 +6481,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>456347</v>
+        <v>456343</v>
       </c>
       <c r="R59" t="n">
-        <v>6796030</v>
+        <v>6796032</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6550,7 +6544,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129725955</v>
+        <v>129725954</v>
       </c>
       <c r="B60" t="n">
         <v>8455</v>
@@ -6594,10 +6588,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>456307</v>
+        <v>456347</v>
       </c>
       <c r="R60" t="n">
-        <v>6795993</v>
+        <v>6796030</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6657,7 +6651,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129725956</v>
+        <v>129725955</v>
       </c>
       <c r="B61" t="n">
         <v>8455</v>
@@ -6701,10 +6695,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>456275</v>
+        <v>456307</v>
       </c>
       <c r="R61" t="n">
-        <v>6795967</v>
+        <v>6795993</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6764,7 +6758,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129725957</v>
+        <v>129725956</v>
       </c>
       <c r="B62" t="n">
         <v>8455</v>
@@ -6808,10 +6802,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>456253</v>
+        <v>456275</v>
       </c>
       <c r="R62" t="n">
-        <v>6795980</v>
+        <v>6795967</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6871,7 +6865,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129725958</v>
+        <v>129725957</v>
       </c>
       <c r="B63" t="n">
         <v>8455</v>
@@ -6915,10 +6909,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>456178</v>
+        <v>456253</v>
       </c>
       <c r="R63" t="n">
-        <v>6795996</v>
+        <v>6795980</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6978,7 +6972,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129725959</v>
+        <v>129725958</v>
       </c>
       <c r="B64" t="n">
         <v>8455</v>
@@ -7022,10 +7016,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>456177</v>
+        <v>456178</v>
       </c>
       <c r="R64" t="n">
-        <v>6795973</v>
+        <v>6795996</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7085,10 +7079,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129726002</v>
+        <v>129725959</v>
       </c>
       <c r="B65" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7096,21 +7090,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7129,10 +7123,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>456047</v>
+        <v>456177</v>
       </c>
       <c r="R65" t="n">
-        <v>6795976</v>
+        <v>6795973</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7192,10 +7186,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129725943</v>
+        <v>129726002</v>
       </c>
       <c r="B66" t="n">
-        <v>97983</v>
+        <v>8444</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7203,34 +7197,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Manmyren, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>456028</v>
+        <v>456047</v>
       </c>
       <c r="R66" t="n">
-        <v>6795975</v>
+        <v>6795976</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,6 +7274,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7289,10 +7293,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134380922</v>
+        <v>135141404</v>
       </c>
       <c r="B67" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7300,21 +7304,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7324,14 +7328,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Hykjeberg, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>456048</v>
+        <v>455958</v>
       </c>
       <c r="R67" t="n">
-        <v>6795965</v>
+        <v>6795854</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7358,12 +7362,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7388,6 +7392,205 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129725943</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Manmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>456028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6795975</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134380922</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Hykjeberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>456048</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6795965</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725975</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725979</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725980</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725981</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725982</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725983</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725984</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725985</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725986</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725987</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725988</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2273,6 +2353,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725989</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2370,6 +2455,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725990</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2476,6 +2566,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725992</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2582,6 +2677,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725993</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2679,6 +2779,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725994</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2785,6 +2890,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725995</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2891,6 +3001,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725996</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2988,6 +3103,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725997</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3089,6 +3209,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658248</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3190,6 +3315,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141614</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3287,6 +3417,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725960</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3384,6 +3519,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725961</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3481,6 +3621,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725913</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3578,6 +3723,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725915</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3675,6 +3825,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725916</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3772,6 +3927,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725917</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3869,6 +4029,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725918</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3966,6 +4131,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725919</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4063,6 +4233,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725920</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4160,6 +4335,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725921</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4257,6 +4437,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725922</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4354,6 +4539,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725923</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4451,6 +4641,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725924</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4548,6 +4743,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725928</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4645,6 +4845,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725929</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4742,6 +4947,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725930</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4847,6 +5057,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725939</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4952,6 +5167,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725940</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5057,6 +5277,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725941</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5162,6 +5387,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725942</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5271,6 +5501,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120805255</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5376,6 +5611,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725932</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5481,6 +5721,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725933</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5586,6 +5831,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725934</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5691,6 +5941,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725935</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5796,6 +6051,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725936</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5901,6 +6161,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134380916</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6006,6 +6271,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725938</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6113,6 +6383,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725948</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6220,6 +6495,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725950</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6327,6 +6607,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725951</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6434,6 +6719,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725952</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6541,6 +6831,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725953</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6648,6 +6943,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725954</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6755,6 +7055,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725955</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6862,6 +7167,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725956</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6969,6 +7279,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725957</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7076,6 +7391,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725958</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7183,6 +7503,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725959</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7290,6 +7615,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726002</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7392,6 +7722,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141404</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7489,6 +7824,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129725943</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7591,8 +7931,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134380922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -3220,7 +3220,7 @@
         <v>135141614</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>135141404</v>
       </c>
       <c r="B67" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 71652-2021 artfynd.xlsx
+++ b/artfynd/A 71652-2021 artfynd.xlsx
@@ -3220,7 +3220,7 @@
         <v>135141614</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>135141404</v>
       </c>
       <c r="B67" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
